--- a/public/contests/ejoy2027/standing_detailed_Day2_en.xlsx
+++ b/public/contests/ejoy2027/standing_detailed_Day2_en.xlsx
@@ -104,7 +104,7 @@
     <t>BGR217</t>
   </si>
   <si>
-    <t>Kaloyan Hristov Ketsarov</t>
+    <t>Kaloyan Hristov Keratsov</t>
   </si>
   <si>
     <t>BGR207</t>
